--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484257_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484257_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9765</v>
+        <v>6.8719</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3246</v>
+        <v>5.2745</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6518</v>
+        <v>1.5974</v>
       </c>
       <c r="G2" t="n">
         <v>3.6031</v>
@@ -610,13 +610,13 @@
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8219</v>
+        <v>-0.9265</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.458</v>
+        <v>-0.5081</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.364</v>
+        <v>-0.4184</v>
       </c>
       <c r="V2" t="n">
         <v>2.4373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.297</v>
+        <v>3.2883</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8503</v>
+        <v>1.2229</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4467</v>
+        <v>2.0654</v>
       </c>
       <c r="G3" t="n">
         <v>1.0079</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4529</v>
+        <v>-0.5558</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5835</v>
+        <v>-0.0438</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1307</v>
+        <v>-0.5119</v>
       </c>
       <c r="V3" t="n">
         <v>1.2735</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8314</v>
+        <v>2.0125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3928</v>
+        <v>0.6556</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4386</v>
+        <v>1.3569</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1824</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0215</v>
+        <v>0.1596</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3218</v>
+        <v>-0.0591</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3003</v>
+        <v>0.2186</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8477</v>
+        <v>1.7333</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0896</v>
+        <v>0.4964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9374</v>
+        <v>1.2369</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4713</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3684</v>
+        <v>-0.4828</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1829</v>
+        <v>-0.5969</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1855</v>
+        <v>0.1141</v>
       </c>
       <c r="V5" t="n">
         <v>3.1014</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0358</v>
+        <v>-0.7972</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2382</v>
+        <v>-0.0999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.274</v>
+        <v>-0.6973</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7077</v>
+        <v>1.1216</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3277</v>
+        <v>-0.254</v>
       </c>
       <c r="I6" t="n">
-        <v>0.62</v>
+        <v>1.3756</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6318</v>
+        <v>0.3973</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7128</v>
+        <v>-0.3044</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>0.7017</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9241</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.385</v>
+        <v>0.0504</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5391</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8254</v>
+        <v>-0.9857</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5657</v>
+        <v>-0.3019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7403</v>
+        <v>-0.6838</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2534</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3322</v>
+        <v>-0.8778</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0788</v>
+        <v>-0.0975</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6077</v>
+        <v>1.0411</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9821</v>
+        <v>0.5283</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5898</v>
+        <v>0.5128</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6334</v>
+        <v>-0.4824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.472</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1054</v>
+        <v>-0.5655</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9743000000000001</v>
+        <v>1.5235</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5102</v>
+        <v>0.4452</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4844</v>
+        <v>1.0784</v>
       </c>
       <c r="P7" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2724</v>
+        <v>-0.8646</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8141</v>
+        <v>-0.6646</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>-2.7145</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2972</v>
+        <v>-1.051</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4638</v>
+        <v>-2.1889</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8334</v>
+        <v>1.1379</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1216</v>
+        <v>-0.7077</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.254</v>
+        <v>-1.3277</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3756</v>
+        <v>0.62</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3973</v>
+        <v>-1.6318</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3044</v>
+        <v>-1.7128</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7017</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.9241</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0504</v>
+        <v>0.385</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5391</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4857</v>
+        <v>-0.2614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>0.615</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.82</v>
+        <v>-0.8764</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4098</v>
+        <v>-1.3793</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-2.0496</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4515</v>
+        <v>0.6703</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0411</v>
+        <v>-1.6077</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5283</v>
+        <v>0.9821</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5128</v>
+        <v>-2.5898</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4824</v>
+        <v>-0.6334</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.472</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5655</v>
+        <v>-1.1054</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5235</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4452</v>
+        <v>0.5102</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0784</v>
+        <v>-1.4844</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2992</v>
+        <v>0.1465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2805</v>
+        <v>-0.2591</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0187</v>
+        <v>0.4056</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7145</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.654</v>
+        <v>-5.9573</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.451</v>
+        <v>-5.7544</v>
       </c>
       <c r="F10" t="n">
         <v>-0.203</v>
@@ -1234,10 +1234,10 @@
         <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3302</v>
+        <v>0.0268</v>
       </c>
       <c r="T10" t="n">
-        <v>0.432</v>
+        <v>0.1287</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2156</v>
+        <v>-6.3771</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4009</v>
+        <v>-4.8348</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8146</v>
+        <v>-1.5423</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2687</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3728</v>
+        <v>-0.5344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8665</v>
+        <v>-0.3004</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5063</v>
+        <v>-0.234</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5507</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.841600000000001</v>
+        <v>-2.631200000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.366199999999999</v>
+        <v>-8.156000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>5.524800000000001</v>
+        <v>5.524699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0688</v>
@@ -1390,13 +1390,13 @@
         <v>17.5808</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.4886</v>
+        <v>-4.2783</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.736</v>
+        <v>-1.5256</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.752899999999999</v>
+        <v>-2.7526</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1675000000000004</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1629</v>
+        <v>3.7792</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3764</v>
+        <v>0.6686</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7865</v>
+        <v>3.1107</v>
       </c>
       <c r="G13" t="n">
         <v>4.1095</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3156</v>
+        <v>0.9319</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1282</v>
+        <v>0.4204</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1874</v>
+        <v>0.5115</v>
       </c>
       <c r="V13" t="n">
         <v>0.8865</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.07</v>
+        <v>3.276</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1831</v>
+        <v>1.5213</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8869</v>
+        <v>1.7547</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3007</v>
+        <v>3.4467</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2763</v>
+        <v>-0.6802</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0245</v>
+        <v>4.1269</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5221</v>
+        <v>1.6541</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7661</v>
+        <v>-1.5299</v>
       </c>
       <c r="L14" t="n">
-        <v>0.756</v>
+        <v>3.184</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7786</v>
+        <v>1.7926</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5102</v>
+        <v>0.8496</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2685</v>
+        <v>0.9429</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8361</v>
+        <v>0.3019</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7046</v>
+        <v>-0.3747</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1316</v>
+        <v>0.6766</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8865</v>
+        <v>-0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4177</v>
+        <v>3.0824</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4202</v>
+        <v>2.0404</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9975000000000001</v>
+        <v>1.042</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4467</v>
+        <v>1.6289</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6802</v>
+        <v>-0.4346</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1269</v>
+        <v>2.0636</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6541</v>
+        <v>0.6453</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5299</v>
+        <v>-0.6102</v>
       </c>
       <c r="L15" t="n">
-        <v>3.184</v>
+        <v>1.2554</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7926</v>
+        <v>0.9837</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8496</v>
+        <v>0.1755</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9429</v>
+        <v>0.8081</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5564</v>
+        <v>0.2469</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4758</v>
+        <v>-0.3073</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0806</v>
+        <v>0.5542</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>2.7693</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.725</v>
+        <v>2.6679</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3326</v>
+        <v>-0.3225</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3924</v>
+        <v>2.9904</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6289</v>
+        <v>2.3007</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4346</v>
+        <v>1.2763</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0636</v>
+        <v>1.0245</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6453</v>
+        <v>1.5221</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6102</v>
+        <v>0.7661</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2554</v>
+        <v>0.756</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9837</v>
+        <v>0.7786</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1755</v>
+        <v>0.5102</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8081</v>
+        <v>0.2685</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1105</v>
+        <v>1.4341</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0151</v>
+        <v>0.199</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0954</v>
+        <v>1.2351</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7693</v>
+        <v>0.8865</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6559</v>
+        <v>0.8865</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9591</v>
+        <v>1.7423</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.396</v>
+        <v>-1.3489</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3551</v>
+        <v>3.0913</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1103</v>
+        <v>2.237</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2988</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1885</v>
+        <v>1.6317</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.2999</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6936</v>
+        <v>-0.449</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7284</v>
+        <v>0.149</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1451</v>
+        <v>2.5369</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3948</v>
+        <v>1.0543</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5399</v>
+        <v>1.4826</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>3.0424</v>
+        <v>0.2868</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9096</v>
+        <v>-0.3142</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1328</v>
+        <v>0.6009</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3869</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8827</v>
+        <v>-0.4827</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4501</v>
+        <v>-2.5082</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3328</v>
+        <v>2.0256</v>
       </c>
       <c r="G18" t="n">
-        <v>2.237</v>
+        <v>-1.1103</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.2988</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6317</v>
+        <v>0.1885</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2999</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.449</v>
+        <v>-1.6936</v>
       </c>
       <c r="L18" t="n">
-        <v>0.149</v>
+        <v>0.7284</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5369</v>
+        <v>-0.1451</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0543</v>
+        <v>0.3948</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4826</v>
+        <v>-0.5399</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5729</v>
+        <v>1.6006</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4153</v>
+        <v>0.7973</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1576</v>
+        <v>0.8033</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6979</v>
+        <v>-0.5304</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2732</v>
+        <v>-1.3453</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.971</v>
+        <v>0.8149</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6816</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0629</v>
+        <v>0.0072</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6186</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5925</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9184</v>
+        <v>0.0819</v>
       </c>
       <c r="L19" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0891</v>
+        <v>-0.3447</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1445</v>
+        <v>-0.0747</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>-0.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3674</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.0032</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.7567</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.3869</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.211</v>
+        <v>-0.5695</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0531</v>
+        <v>0.3743</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8421</v>
+        <v>-0.9438</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-2.6816</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0072</v>
+        <v>-1.0629</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-1.6186</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-1.5925</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0819</v>
+        <v>-0.9184</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3447</v>
+        <v>-1.0891</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0747</v>
+        <v>-0.1445</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.27</v>
+        <v>-0.9445</v>
       </c>
       <c r="P20" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.274</v>
+        <v>1.1316</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>0.8579</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2102</v>
+        <v>0.2737</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3071</v>
+        <v>-2.2156</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8538</v>
+        <v>-3.8427</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5467</v>
+        <v>1.6271</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6104</v>
@@ -2092,13 +2092,13 @@
         <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5013</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.2849</v>
       </c>
       <c r="U21" t="n">
-        <v>0.225</v>
+        <v>0.3053</v>
       </c>
       <c r="V21" t="n">
         <v>0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1599</v>
+        <v>-4.2117</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3573</v>
+        <v>-0.7617</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8027</v>
+        <v>-3.4499</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3146</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3065</v>
+        <v>1.2547</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3703</v>
+        <v>0.9659</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0639</v>
+        <v>0.2888</v>
       </c>
       <c r="V22" t="n">
         <v>-3.9331</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.841499999999998</v>
+        <v>6.537899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5248</v>
+        <v>-5.5247</v>
       </c>
       <c r="F23" t="n">
-        <v>9.366300000000001</v>
+        <v>12.063</v>
       </c>
       <c r="G23" t="n">
         <v>3.0689</v>
@@ -2218,7 +2218,7 @@
         <v>1.0477</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0215</v>
+        <v>2.021499999999998</v>
       </c>
       <c r="J23" t="n">
         <v>-0.4487000000000004</v>
@@ -2248,13 +2248,13 @@
         <v>12.6974</v>
       </c>
       <c r="S23" t="n">
-        <v>5.488700000000001</v>
+        <v>8.1852</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7527</v>
+        <v>2.7528</v>
       </c>
       <c r="U23" t="n">
-        <v>2.736000000000001</v>
+        <v>5.432300000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0.1674999999999991</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484257_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484257_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.1097</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-9.751900000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,11 +2205,16 @@
       <c r="X21" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2186,6 +2287,11 @@
       </c>
       <c r="X22" t="n">
         <v>-3.9331</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484257_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-9.5844</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
